--- a/examples/output/part2_results.xlsx
+++ b/examples/output/part2_results.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>["HTTP 200; ответ 211 байт; извлечено 45 символов.", "Проблемы извлечения: "]</t>
+          <t>["HTTP 200; ответ 211 байт; извлечено 45 символов."]</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AR8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:08:26+00:00</t>
+          <t>2026-10-17T08:47:00+00:00</t>
         </is>
       </c>
     </row>

--- a/examples/output/part2_results.xlsx
+++ b/examples/output/part2_results.xlsx
@@ -722,12 +722,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -799,18 +799,22 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
+          <t>book_4e377ef9865aaadb</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic library</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>["DemoBook Amber 101"]</t>
+          <t>["DemoBook Aurora 101"]</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>["Mira Placeholder"]</t>
+          <t>["Avery Demo"]</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -834,25 +838,25 @@
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>{"state": "matched", "book_id": "book_74e3f59c074a5cda", "unresolved_signals": [], "detected_formats": ["ebook"], "identity_evidence": ["primary: DemoBook Amber 101", "Автор: Mira Placeholder"], "other_catalog_matches": []}</t>
+          <t>{"state": "matched", "book_id": "book_4e377ef9865aaadb", "unresolved_signals": [], "detected_formats": ["ebook"], "identity_evidence": ["primary: DemoBook Aurora 101", "Автор: Avery Demo"], "other_catalog_matches": []}</t>
         </is>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101 Mira Placeholder A synthetic catalog entry for a fictional training book. Download EPUB</t>
+          <t>DemoBook Aurora 101 Avery Demo Fictional training edition. Synthetic library catalog. Available reading formats are listed below. Download EPUB</t>
         </is>
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>[{"kind": "file_link", "format": "ebook", "url": "https://library.example/files/amber.epub", "detail": "Ссылка на файл epub: Download EPUB", "binding": "bound", "scope_title": "DemoBook Amber 101", "document_url": "https://library.example/own.html", "raw_resource": "/files/amber.epub", "semantic_role": "book", "scope_authors": ["Mira Placeholder"], "scope_locator": "article", "element_locator": "a", "binding_reason": "Область с заголовком проверяемой книги; вложенные области проверены."}]</t>
+          <t>[{"kind": "file_link", "format": "ebook", "url": "https://library.example/files/aurora.epub", "detail": "Ссылка на файл epub: Download EPUB", "binding": "bound", "scope_title": "DemoBook Aurora 101", "document_url": "https://library.example/own.html", "raw_resource": "/files/aurora.epub", "semantic_role": "book", "scope_authors": ["Avery Demo"], "scope_locator": "article.book-card", "element_locator": "a", "binding_reason": "Область с заголовком проверяемой книги; вложенные области проверены."}]</t>
         </is>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>["primary: DemoBook Amber 101", "Автор: Mira Placeholder", "Ссылка на файл epub: Download EPUB https://library.example/files/amber.epub Область: article; заголовок: DemoBook Amber 101."]</t>
+          <t>["primary: DemoBook Aurora 101", "Автор: Avery Demo", "Ссылка на файл epub: Download EPUB https://library.example/files/aurora.epub Область: article.book-card; заголовок: DemoBook Aurora 101."]</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
@@ -862,12 +866,12 @@
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>[{"kind": "file_link", "format": "ebook", "url": "https://library.example/files/amber.epub", "detail": "Ссылка на файл epub: Download EPUB", "binding": "bound", "scope_title": "DemoBook Amber 101", "document_url": "https://library.example/own.html", "raw_resource": "/files/amber.epub", "semantic_role": "book", "scope_authors": ["Mira Placeholder"], "scope_locator": "article", "element_locator": "a", "binding_reason": "Область с заголовком проверяемой книги; вложенные области проверены."}]</t>
+          <t>[{"kind": "file_link", "format": "ebook", "url": "https://library.example/files/aurora.epub", "detail": "Ссылка на файл epub: Download EPUB", "binding": "bound", "scope_title": "DemoBook Aurora 101", "document_url": "https://library.example/own.html", "raw_resource": "/files/aurora.epub", "semantic_role": "book", "scope_authors": ["Avery Demo"], "scope_locator": "article.book-card", "element_locator": "a", "binding_reason": "Область с заголовком проверяемой книги; вложенные области проверены."}]</t>
         </is>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>[{"label": "Download EPUB", "url": "https://library.example/files/amber.epub"}]</t>
+          <t>[{"label": "Download EPUB", "url": "https://library.example/files/aurora.epub"}]</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
@@ -882,14 +886,14 @@
         </is>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>296</v>
+        <v>385</v>
       </c>
       <c r="AQ2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +918,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -929,7 +933,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -984,15 +988,19 @@
         </is>
       </c>
       <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic library</t>
+        </is>
+      </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>["DemoBook Copper 202"]</t>
+          <t>["DemoBook Boreal 202"]</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>["Owen Sample"]</t>
+          <t>["Robin Sample"]</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1020,11 +1028,11 @@
         </is>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="AG3" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Copper 202 Owen Sample Download EPUB</t>
+          <t>DemoBook Boreal 202 Robin Sample Fictional training edition. Synthetic library catalog. Available reading formats are listed below. Download EPUB</t>
         </is>
       </c>
       <c r="AH3" s="2" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>["HTTP 200; ответ 211 байт; извлечено 45 символов."]</t>
+          <t>["Извлечённый заголовок: Synthetic library", "Извлечённые авторы: Robin Sample"]</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="inlineStr">
@@ -1044,12 +1052,12 @@
       </c>
       <c r="AK3" s="2" t="inlineStr">
         <is>
-          <t>[{"kind": "file_link", "format": "ebook", "url": "https://library.example/files/copper.epub", "detail": "Ссылка на файл epub: Download EPUB", "binding": "bound", "scope_title": "DemoBook Copper 202", "document_url": "https://library.example/foreign.html", "raw_resource": "/files/copper.epub", "semantic_role": "book", "scope_authors": ["Owen Sample"], "scope_locator": "main", "element_locator": "a", "binding_reason": "Область с заголовком проверяемой книги; вложенные области проверены."}]</t>
+          <t>[{"kind": "file_link", "format": "ebook", "url": "https://library.example/files/boreal.epub", "detail": "Ссылка на файл epub: Download EPUB", "binding": "bound", "scope_title": "DemoBook Boreal 202", "document_url": "https://library.example/foreign.html", "raw_resource": "/files/boreal.epub", "semantic_role": "book", "scope_authors": ["Robin Sample"], "scope_locator": "article.book-card", "element_locator": "a", "binding_reason": "Область с заголовком проверяемой книги; вложенные области проверены."}]</t>
         </is>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>[{"label": "Download EPUB", "url": "https://library.example/files/copper.epub"}]</t>
+          <t>[{"label": "Download EPUB", "url": "https://library.example/files/boreal.epub"}]</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
@@ -1064,14 +1072,14 @@
         </is>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>211</v>
+        <v>387</v>
       </c>
       <c r="AQ3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1104,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1111,7 +1119,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -1127,12 +1135,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>content_requires_js</t>
+          <t>loading_shell</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Заявлены чтение/плеер, но связанное содержимое ещё не получено; требуется браузерная проверка.</t>
+          <t>Получена загрузочная оболочка: содержимое книги ещё не доступно для анализа.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1145,7 +1153,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>{"http_status": 200, "final_url": "https://library.example/uncertain.html", "error": "", "status": 2, "reason_code": "content_requires_js"}</t>
+          <t>{"http_status": 200, "final_url": "https://library.example/uncertain.html", "error": "", "status": 2, "reason_code": "loading_shell"}</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1153,38 +1161,32 @@
           <t>{"attempted": false, "ready": false, "reason": "Не требуется или отключён."}</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>ebook</t>
-        </is>
-      </c>
+      <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="T4" s="2" t="b">
-        <v>0</v>
-      </c>
+      <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>unavailable</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>book_74e3f59c074a5cda</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>["DemoBook Amber 101"]</t>
+          <t>["Loading"]</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>["Mira Placeholder"]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1208,15 +1210,15 @@
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>{"state": "unavailable", "book_id": "book_74e3f59c074a5cda", "unresolved_signals": [], "detected_formats": [], "identity_evidence": ["primary: DemoBook Amber 101", "Автор: Mira Placeholder"], "other_catalog_matches": []}</t>
+          <t>{"state": "unavailable", "book_id": null, "identity_evidence": [], "other_catalog_matches": []}</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101 Mira Placeholder Loading</t>
+          <t>Loading Please enable JavaScript. Book content is loading.</t>
         </is>
       </c>
       <c r="AH4" s="2" t="inlineStr">
@@ -1226,12 +1228,12 @@
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>["primary: DemoBook Amber 101", "Автор: Mira Placeholder"]</t>
+          <t>["Извлечённый заголовок: Loading", "Извлечённые авторы: "]</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>["content_requires_js"]</t>
+          <t>["loading_shell", "content_requires_js"]</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr">
@@ -1256,14 +1258,14 @@
         </is>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="AQ4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1290,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1303,7 +1305,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -1365,12 +1367,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
@@ -1380,12 +1382,12 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>["Mira Placeholder"]</t>
+          <t>["Avery Demo"]</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>{"/Producer": "pypdf", "/Title": "DemoBook Amber 101", "/Author": "Mira Placeholder"}</t>
+          <t>{"/Producer": "pypdf", "/Title": "DemoBook Aurora 101", "/Author": "Avery Demo", "/Creator": "Synthetic demo generator"}</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1404,25 +1406,25 @@
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>{"state": "matched", "book_id": "book_74e3f59c074a5cda", "unresolved_signals": [], "detected_formats": ["ebook"], "identity_evidence": ["pdf_metadata: DemoBook Amber 101", "Автор: Mira Placeholder"], "other_catalog_matches": []}</t>
+          <t>{"state": "matched", "book_id": "book_4e377ef9865aaadb", "unresolved_signals": [], "detected_formats": ["ebook"], "identity_evidence": ["pdf_metadata: DemoBook Aurora 101", "Автор: Avery Demo"], "other_catalog_matches": []}</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>3911</v>
+        <v>5093</v>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101 Mira Placeholder The traveler walked north and reached the bridge before sunset. The traveler walked north and reached the bridge before sunset. The traveler walked north and reached the bridge before sunset. The traveler</t>
+          <t>DemoBook Aurora 101 Avery Demo Chapter 1 The traveler crossed the quiet bridge and opened a small notebook beside the river. A lantern marked the path ahead while distant bells announced the evening arrival. The traveler crossed the quiet b</t>
         </is>
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/own.pdf", "detail": "Из PDF извлечено 3911 символов, страниц 2/2; полнота книги не установлена."}]</t>
+          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/own.pdf", "detail": "Из PDF извлечено 5093 символов, страниц 2/2; полнота книги не установлена."}]</t>
         </is>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>["pdf_metadata: DemoBook Amber 101", "Автор: Mira Placeholder", "Из PDF извлечено 3911 символов, страниц 2/2; полнота книги не установлена. https://library.example/own.pdf"]</t>
+          <t>["pdf_metadata: DemoBook Aurora 101", "Автор: Avery Demo", "Из PDF извлечено 5093 символов, страниц 2/2; полнота книги не установлена. https://library.example/own.pdf"]</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr">
@@ -1432,7 +1434,7 @@
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/own.pdf", "detail": "Из PDF извлечено 3911 символов, страниц 2/2; полнота книги не установлена."}]</t>
+          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/own.pdf", "detail": "Из PDF извлечено 5093 символов, страниц 2/2; полнота книги не установлена."}]</t>
         </is>
       </c>
       <c r="AL5" s="2" t="inlineStr">
@@ -1452,14 +1454,14 @@
         </is>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>5849</v>
+        <v>6632</v>
       </c>
       <c r="AQ5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1486,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1499,7 +1501,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -1556,7 +1558,7 @@
       <c r="V6" s="2" t="n"/>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Copper 202</t>
+          <t>DemoBook Boreal 202</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
@@ -1566,12 +1568,12 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>["Owen Sample"]</t>
+          <t>["Robin Sample"]</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>{"/Producer": "pypdf", "/Title": "DemoBook Copper 202", "/Author": "Owen Sample"}</t>
+          <t>{"/Producer": "pypdf", "/Title": "DemoBook Boreal 202", "/Author": "Robin Sample", "/Creator": "Synthetic demo generator"}</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1594,11 +1596,11 @@
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>3903</v>
+        <v>5097</v>
       </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Copper 202 Owen Sample The traveler walked north and reached the bridge before sunset. The traveler walked north and reached the bridge before sunset. The traveler walked north and reached the bridge before sunset. The traveler wal</t>
+          <t>DemoBook Boreal 202 Robin Sample Chapter 1 The traveler crossed the quiet bridge and opened a small notebook beside the river. A lantern marked the path ahead while distant bells announced the evening arrival. The traveler crossed the quiet</t>
         </is>
       </c>
       <c r="AH6" s="2" t="inlineStr">
@@ -1608,7 +1610,7 @@
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>["Извлечённый заголовок: DemoBook Copper 202", "Извлечённые авторы: Owen Sample"]</t>
+          <t>["Извлечённый заголовок: DemoBook Boreal 202", "Извлечённые авторы: Robin Sample"]</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr">
@@ -1618,7 +1620,7 @@
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/foreign.pdf", "detail": "Из PDF извлечено 3903 символов, страниц 2/2; полнота книги не установлена."}]</t>
+          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/foreign.pdf", "detail": "Из PDF извлечено 5097 символов, страниц 2/2; полнота книги не установлена."}]</t>
         </is>
       </c>
       <c r="AL6" s="2" t="inlineStr">
@@ -1638,14 +1640,14 @@
         </is>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>5837</v>
+        <v>6638</v>
       </c>
       <c r="AQ6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1672,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1685,7 +1687,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -1706,7 +1708,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>PDF идентифицирует книгу, но обозначен как рецензия или критический разбор; текст произведения не подтверждён.</t>
+          <t>PDF идентифицирует книгу, но имеются признаки пересказа, рецензии, критического разбора или учебных материалов; текст произведения не подтверждён.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1747,12 +1749,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
@@ -1762,12 +1764,12 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>["Mira Placeholder"]</t>
+          <t>["Avery Demo"]</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>{"/Producer": "pypdf", "/Title": "DemoBook Amber 101", "/Author": "Mira Placeholder", "/Subject": "Book review", "document_role": "review"}</t>
+          <t>{"/Producer": "pypdf", "/Title": "DemoBook Aurora 101", "/Author": "Avery Demo", "/Creator": "Synthetic demo generator", "/Subject": "Book review", "document_role": "review", "document_role_evidence": "Book review"}</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1786,15 +1788,15 @@
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>{"state": "matched", "book_id": "book_74e3f59c074a5cda", "unresolved_signals": [], "detected_formats": [], "identity_evidence": ["pdf_metadata: DemoBook Amber 101", "Автор: Mira Placeholder"], "other_catalog_matches": []}</t>
+          <t>{"state": "matched", "book_id": "book_4e377ef9865aaadb", "unresolved_signals": [{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/review.pdf", "detail": "Из PDF извлечено 4367 символов, страниц 2/2; полнота книги не установлена.", "binding": "unresolved", "binding_reason": "Роль PDF не подтверждает текст произведения: Book review"}], "detected_formats": [], "identity_evidence": ["pdf_metadata: DemoBook Aurora 101", "Автор: Avery Demo"], "other_catalog_matches": []}</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>3935</v>
+        <v>4367</v>
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DemoBook Amber 101 Mira Placeholder Book review The traveler walked north and reached the bridge before sunset. The traveler walked north and reached the bridge before sunset. The traveler walked north and reached the bridge before sunset. </t>
+          <t xml:space="preserve">DemoBook Aurora 101 Avery Demo Book review This review discusses the plot and characters of the novel. The reviewer examines the imaginary journey and gives an opinion on its themes. The reviewer examines the imaginary journey and gives an </t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
@@ -1804,7 +1806,7 @@
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>["pdf_metadata: DemoBook Amber 101", "Автор: Mira Placeholder"]</t>
+          <t>["pdf_metadata: DemoBook Aurora 101", "Автор: Avery Demo", "Признаки роли PDF: Book review"]</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
@@ -1814,7 +1816,7 @@
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"kind": "pdf_text", "format": "ebook", "url": "https://library.example/review.pdf", "detail": "Из PDF извлечено 4367 символов, страниц 2/2; полнота книги не установлена.", "binding": "unresolved", "binding_reason": "Роль PDF не подтверждает текст произведения: Book review"}]</t>
         </is>
       </c>
       <c r="AL7" s="2" t="inlineStr">
@@ -1834,14 +1836,14 @@
         </is>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>5924</v>
+        <v>5881</v>
       </c>
       <c r="AQ7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Mira Placeholder</t>
+          <t>Avery Demo</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>DemoBook Amber 101</t>
+          <t>DemoBook Aurora 101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1881,7 +1883,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>book_74e3f59c074a5cda</t>
+          <t>book_4e377ef9865aaadb</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1936,7 +1938,11 @@
         </is>
       </c>
       <c r="V8" s="2" t="n"/>
-      <c r="W8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic library</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1972,11 +1978,11 @@
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="AG8" s="2" t="inlineStr">
         <is>
-          <t>Loading</t>
+          <t>Loading. Please enable JavaScript.</t>
         </is>
       </c>
       <c r="AH8" s="2" t="inlineStr">
@@ -1986,7 +1992,7 @@
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>["HTTP 200; ответ 445 байт; извлечено 7 символов.", "Проблемы извлечения: content_requires_js, insufficient_html"]</t>
+          <t>["Извлечённый заголовок: Synthetic library", "Извлечённые авторы: "]</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr">
@@ -2016,14 +2022,14 @@
         </is>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>445</v>
+        <v>583</v>
       </c>
       <c r="AQ8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:00+00:00</t>
+          <t>2026-10-29T17:31:45+00:00</t>
         </is>
       </c>
     </row>

--- a/examples/output/part2_results.xlsx
+++ b/examples/output/part2_results.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="AR2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AR3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AR4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AR5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AR6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AR7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AR8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T17:31:45+00:00</t>
+          <t>2026-10-31T11:45:15+00:00</t>
         </is>
       </c>
     </row>
